--- a/data/trans_orig/P19C09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C09-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2007 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22939</t>
+          <t>23191</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32510</t>
+          <t>33877</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25579</t>
+          <t>26330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>51025</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>454898</t>
+          <t>454646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470043</t>
+          <t>469380</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>505594</t>
+          <t>504227</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>523861</t>
+          <t>523412</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>966321</t>
+          <t>964916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>990362</t>
+          <t>989611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27681</t>
+          <t>28471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>17619</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39294</t>
+          <t>38403</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31661</t>
+          <t>31126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58212</t>
+          <t>58565</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>694447</t>
+          <t>693657</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>711920</t>
+          <t>711203</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>764932</t>
+          <t>765823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>785437</t>
+          <t>786607</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1468142</t>
+          <t>1467789</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1494693</t>
+          <t>1495228</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24312</t>
+          <t>23565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24201</t>
+          <t>24252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>19472</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41373</t>
+          <t>41004</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519736</t>
+          <t>520483</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536444</t>
+          <t>536462</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>560408</t>
+          <t>560357</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>575843</t>
+          <t>575102</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1087284</t>
+          <t>1087653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1108956</t>
+          <t>1109185</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28916</t>
+          <t>28647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>13552</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>32288</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27344</t>
+          <t>29026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53140</t>
+          <t>52290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>677561</t>
+          <t>677830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>695222</t>
+          <t>695175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>776721</t>
+          <t>778028</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>796806</t>
+          <t>796764</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1463653</t>
+          <t>1464503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1489449</t>
+          <t>1487767</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49747</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80395</t>
+          <t>80461</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69534</t>
+          <t>68707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106829</t>
+          <t>105070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126092</t>
+          <t>127168</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178096</t>
+          <t>175380</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2370096</t>
+          <t>2370030</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2400744</t>
+          <t>2400680</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2630426</t>
+          <t>2632185</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2667721</t>
+          <t>2668548</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5009649</t>
+          <t>5012365</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5061653</t>
+          <t>5060577</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2012 (tasa de respuesta: 97,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20231</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20791</t>
+          <t>20642</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13732</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>32190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>571958</t>
+          <t>572129</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>587192</t>
+          <t>587041</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>605807</t>
+          <t>605956</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>620670</t>
+          <t>620516</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1184920</t>
+          <t>1186597</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1205055</t>
+          <t>1205041</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20255</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>17332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38079</t>
+          <t>39055</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28716</t>
+          <t>27265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54537</t>
+          <t>52722</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>824332</t>
+          <t>824307</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>838402</t>
+          <t>838282</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>847973</t>
+          <t>846997</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>869748</t>
+          <t>868720</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1676102</t>
+          <t>1677917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1701923</t>
+          <t>1703374</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17219</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>9430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27559</t>
+          <t>27104</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>16340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38889</t>
+          <t>37835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609562</t>
+          <t>609554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622760</t>
+          <t>622774</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>630198</t>
+          <t>630653</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>648233</t>
+          <t>648327</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1245649</t>
+          <t>1246703</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1268736</t>
+          <t>1268198</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10268</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29606</t>
+          <t>28466</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19997</t>
+          <t>20768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43960</t>
+          <t>45561</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35749</t>
+          <t>36750</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65187</t>
+          <t>66956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>743557</t>
+          <t>744697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>762699</t>
+          <t>762895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>855816</t>
+          <t>854215</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>879779</t>
+          <t>879008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1607752</t>
+          <t>1605983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1637190</t>
+          <t>1636189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35840</t>
+          <t>34584</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65963</t>
+          <t>63186</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68765</t>
+          <t>66714</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106697</t>
+          <t>105433</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114248</t>
+          <t>111290</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163248</t>
+          <t>159439</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2770756</t>
+          <t>2773533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2800879</t>
+          <t>2802135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2963487</t>
+          <t>2964751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3001419</t>
+          <t>3003470</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5743655</t>
+          <t>5747464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5792655</t>
+          <t>5795613</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10406</t>
+          <t>10046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27438</t>
+          <t>27293</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19768</t>
+          <t>20892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19790</t>
+          <t>19034</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42388</t>
+          <t>41833</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>497555</t>
+          <t>497700</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>514587</t>
+          <t>514947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>524595</t>
+          <t>523471</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>538601</t>
+          <t>537885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1026968</t>
+          <t>1027523</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1049566</t>
+          <t>1050322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>31654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18506</t>
+          <t>17711</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40725</t>
+          <t>39944</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37066</t>
+          <t>37867</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64231</t>
+          <t>64866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>783502</t>
+          <t>784692</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>802307</t>
+          <t>802384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>825648</t>
+          <t>826429</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>847867</t>
+          <t>848662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1618488</t>
+          <t>1617853</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1645653</t>
+          <t>1644852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26473</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>15221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>14737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33987</t>
+          <t>33337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>523887</t>
+          <t>524742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541098</t>
+          <t>541428</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>565432</t>
+          <t>564517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>576669</t>
+          <t>576697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1096111</t>
+          <t>1096761</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1116244</t>
+          <t>1115361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14010</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32348</t>
+          <t>32805</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>20497</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43498</t>
+          <t>44778</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38164</t>
+          <t>38190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66955</t>
+          <t>66662</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>740287</t>
+          <t>739830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>758625</t>
+          <t>758849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>833343</t>
+          <t>832063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>856825</t>
+          <t>856344</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1582521</t>
+          <t>1582814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1611312</t>
+          <t>1611286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>61511</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96900</t>
+          <t>96961</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59388</t>
+          <t>59852</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95811</t>
+          <t>96283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128980</t>
+          <t>130042</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>177268</t>
+          <t>179356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2567433</t>
+          <t>2567372</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2603182</t>
+          <t>2602822</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2771504</t>
+          <t>2771032</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2807927</t>
+          <t>2807463</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5354380</t>
+          <t>5352292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5402668</t>
+          <t>5401606</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C09-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23191</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33877</t>
+          <t>34193</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26330</t>
+          <t>26056</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51025</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>454646</t>
+          <t>455657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>469380</t>
+          <t>469254</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>504227</t>
+          <t>503911</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>523412</t>
+          <t>523008</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>964916</t>
+          <t>964623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>989611</t>
+          <t>989885</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10925</t>
+          <t>9739</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28471</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17619</t>
+          <t>18172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38403</t>
+          <t>38349</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31126</t>
+          <t>31835</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58565</t>
+          <t>59192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>693657</t>
+          <t>694953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>711203</t>
+          <t>712389</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>765823</t>
+          <t>765877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>786607</t>
+          <t>786054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1467789</t>
+          <t>1467162</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1495228</t>
+          <t>1494519</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23565</t>
+          <t>24604</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19472</t>
+          <t>19453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41004</t>
+          <t>41667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520483</t>
+          <t>519444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536462</t>
+          <t>536818</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>560357</t>
+          <t>560326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>575102</t>
+          <t>575543</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1087653</t>
+          <t>1086990</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1109185</t>
+          <t>1109204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28647</t>
+          <t>28645</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13552</t>
+          <t>13185</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>32007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29026</t>
+          <t>28936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52290</t>
+          <t>54292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>677830</t>
+          <t>677832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>695175</t>
+          <t>694702</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>778028</t>
+          <t>778309</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>796764</t>
+          <t>797131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1464503</t>
+          <t>1462501</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1487767</t>
+          <t>1487857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49811</t>
+          <t>49727</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80461</t>
+          <t>81908</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68707</t>
+          <t>69568</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105070</t>
+          <t>105202</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127168</t>
+          <t>126470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175380</t>
+          <t>175335</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2370030</t>
+          <t>2368583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2400680</t>
+          <t>2400764</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2632185</t>
+          <t>2632053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2668548</t>
+          <t>2667687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5012365</t>
+          <t>5012410</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5060577</t>
+          <t>5061275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20642</t>
+          <t>20494</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32190</t>
+          <t>33559</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>572129</t>
+          <t>572602</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>587041</t>
+          <t>587326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>605956</t>
+          <t>606104</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>620516</t>
+          <t>620495</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1186597</t>
+          <t>1185228</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1205041</t>
+          <t>1205114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>21072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17332</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39055</t>
+          <t>38760</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>26854</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52722</t>
+          <t>53273</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>824307</t>
+          <t>823515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>838282</t>
+          <t>837743</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>846997</t>
+          <t>847292</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>868720</t>
+          <t>869372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1677917</t>
+          <t>1677366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1703374</t>
+          <t>1703785</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17227</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>9341</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27104</t>
+          <t>26561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16340</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37835</t>
+          <t>38774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609554</t>
+          <t>610319</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622774</t>
+          <t>622790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>630653</t>
+          <t>631196</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>648327</t>
+          <t>648416</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1246703</t>
+          <t>1245764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1268198</t>
+          <t>1267654</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28466</t>
+          <t>29021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>20854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45561</t>
+          <t>44108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36750</t>
+          <t>35947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66956</t>
+          <t>65181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>744697</t>
+          <t>744142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>762895</t>
+          <t>762973</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>854215</t>
+          <t>855668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>879008</t>
+          <t>878922</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1605983</t>
+          <t>1607758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1636189</t>
+          <t>1636992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>36997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63186</t>
+          <t>66974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66714</t>
+          <t>69078</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105433</t>
+          <t>106971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111290</t>
+          <t>111187</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159439</t>
+          <t>160618</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2773533</t>
+          <t>2769745</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2802135</t>
+          <t>2799722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2964751</t>
+          <t>2963213</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3003470</t>
+          <t>3001106</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5747464</t>
+          <t>5746285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5795613</t>
+          <t>5795716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27293</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20892</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19034</t>
+          <t>19442</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41833</t>
+          <t>43012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>497700</t>
+          <t>498630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>523471</t>
+          <t>524203</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>537885</t>
+          <t>538067</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1027523</t>
+          <t>1026344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1050322</t>
+          <t>1049914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>13787</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31654</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17711</t>
+          <t>18301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39944</t>
+          <t>41294</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37867</t>
+          <t>36828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64866</t>
+          <t>65639</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>784692</t>
+          <t>784464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>802384</t>
+          <t>802559</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>826429</t>
+          <t>825079</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>848662</t>
+          <t>848072</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1617853</t>
+          <t>1617080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1644852</t>
+          <t>1645891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25618</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15221</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14737</t>
+          <t>14515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33337</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>524742</t>
+          <t>525038</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541428</t>
+          <t>541343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>564517</t>
+          <t>565332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>576697</t>
+          <t>576750</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1096761</t>
+          <t>1097109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1115361</t>
+          <t>1115583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32805</t>
+          <t>33064</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20497</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44778</t>
+          <t>43254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38190</t>
+          <t>39610</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66662</t>
+          <t>67707</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>739830</t>
+          <t>739571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>758849</t>
+          <t>758278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>832063</t>
+          <t>833587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>856344</t>
+          <t>857152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1582814</t>
+          <t>1581769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1611286</t>
+          <t>1609866</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61511</t>
+          <t>60098</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96961</t>
+          <t>94125</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59852</t>
+          <t>61045</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96283</t>
+          <t>97964</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130042</t>
+          <t>130383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>179356</t>
+          <t>180676</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2567372</t>
+          <t>2570208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2602822</t>
+          <t>2604235</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2771032</t>
+          <t>2769351</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2807463</t>
+          <t>2806270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5352292</t>
+          <t>5350972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5401606</t>
+          <t>5401265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
